--- a/tools/importer/reports/import-turner-home.report.xlsx
+++ b/tools/importer/reports/import-turner-home.report.xlsx
@@ -151,7 +151,7 @@
     <t>tangent-energy/en-us</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:22.410Z</t>
+    <t>2026-08-24T08:03:38.972Z</t>
   </si>
   <si>
     <t>turner-powertrain/en-us.report.json</t>
@@ -166,7 +166,7 @@
     <t>turner-home</t>
   </si>
   <si>
-    <t>2026-08-24T06:45:38.864Z</t>
+    <t>2026-08-24T08:04:27.919Z</t>
   </si>
   <si>
     <t>Turner | Turner Power Train</t>
@@ -181,7 +181,7 @@
     <t>tangent-energy/en-us/about-us</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:28.865Z</t>
+    <t>2026-08-24T08:03:48.169Z</t>
   </si>
   <si>
     <t>tangent-energy/en-us/customer-segments.report.json</t>
@@ -190,7 +190,7 @@
     <t>tangent-energy/en-us/customer-segments</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:44.951Z</t>
+    <t>2026-08-24T08:04:08.234Z</t>
   </si>
   <si>
     <t>tangent-energy/en-us/meet-the-team.report.json</t>
@@ -199,7 +199,7 @@
     <t>tangent-energy/en-us/meet-the-team</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:36.480Z</t>
+    <t>2026-08-24T08:03:58.674Z</t>
   </si>
   <si>
     <t>tangent-energy/en-us/tangent-amp.report.json</t>
@@ -208,7 +208,7 @@
     <t>tangent-energy/en-us/tangent-amp</t>
   </si>
   <si>
-    <t>2026-08-22T12:54:52.259Z</t>
+    <t>2026-08-24T08:04:17.475Z</t>
   </si>
   <si>
     <t>turner-powertrain/en-us/about-us.report.json</t>
@@ -244,7 +244,7 @@
     <t>turner-knowledge-hub</t>
   </si>
   <si>
-    <t>2026-08-24T06:44:10.311Z</t>
+    <t>2026-08-24T06:45:48.248Z</t>
   </si>
   <si>
     <t>Knowledge Hub | Turner Power Train</t>
